--- a/GRAVITY.xlsx
+++ b/GRAVITY.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ydauser01\Documents\_Git\Gravity\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7002BFCE-812A-45B8-9733-96B988B1FD31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D273FD88-6493-4E15-82B7-D4725CF8D03C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1752" yWindow="1524" windowWidth="19008" windowHeight="10728" xr2:uid="{66840920-CFD3-4837-8A93-7C4CBF5AB457}"/>
+    <workbookView xWindow="3744" yWindow="1296" windowWidth="17280" windowHeight="10500" xr2:uid="{66840920-CFD3-4837-8A93-7C4CBF5AB457}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -42,150 +42,129 @@
     <t>ゲームとして最低限遊べる</t>
   </si>
   <si>
+    <t>重力で遊べる</t>
+  </si>
+  <si>
+    <t>考えて進む要素</t>
+  </si>
+  <si>
+    <t>完成度UP</t>
+  </si>
+  <si>
+    <t>完成</t>
+  </si>
+  <si>
+    <t>歩いてクリアできる</t>
+  </si>
+  <si>
+    <t>重力使わないと進めない</t>
+  </si>
+  <si>
+    <t>考えて進める</t>
+  </si>
+  <si>
+    <t>最初から最後まで遊べる</t>
+  </si>
+  <si>
+    <t>人に見せられる</t>
+  </si>
+  <si>
+    <t>7/16提出可能</t>
+  </si>
+  <si>
+    <t>最低限ゲーム</t>
+  </si>
+  <si>
+    <t>ゲームの核完成</t>
+  </si>
+  <si>
+    <t>ゲームらしくなる</t>
+  </si>
+  <si>
+    <t>中間発表レベル</t>
+  </si>
+  <si>
+    <t>発表可能</t>
+  </si>
+  <si>
     <t>週</t>
-    <rPh sb="0" eb="1">
-      <t>シュウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>目標</t>
-    <rPh sb="0" eb="2">
-      <t>モクヒョウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>やること（詳細）</t>
-    <rPh sb="5" eb="7">
-      <t>ショウサイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>完成条件</t>
-    <rPh sb="0" eb="4">
-      <t>カンセイジョウケン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>週末状況</t>
-    <rPh sb="0" eb="4">
-      <t>シュウマツジョウキョウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>第6週</t>
-  </si>
-  <si>
-    <t>重力で遊べる</t>
-  </si>
-  <si>
-    <t>考えて進む要素</t>
+  </si>
+  <si>
+    <r>
+      <t>第1週</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>〜今週末</t>
+    </r>
+  </si>
+  <si>
+    <t>カメラ完成（追従・マウス視点・角度調整）仮マップ作成（Cubeのみ）ゴール判定（Trigger）</t>
+  </si>
+  <si>
+    <t>第2週</t>
+  </si>
+  <si>
+    <t>重力切替プレイヤー180度回転カメラ連動重力を使う地形作成</t>
+  </si>
+  <si>
+    <t>第3週</t>
+  </si>
+  <si>
+    <t>箱＋スイッチ扉開閉パズル構成</t>
+  </si>
+  <si>
+    <t>第4週</t>
   </si>
   <si>
     <t>1ステージ完成</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>完成度UP</t>
-  </si>
-  <si>
-    <t>完成</t>
-  </si>
-  <si>
-    <t>テスト バグ修正 発表準備</t>
-  </si>
-  <si>
-    <t>カメラ完成（追従・マウス視点・角度調整）
-仮マップ作成（Cubeのみ）
-ゴール判定（Trigger）</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>重力切替
-プレイヤー180度回転
-カメラ連動
-重力を使う地形作成</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>箱＋スイッチ
-扉開閉
-パズル構成</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>エリア配置
-導線調整
-難易度調整</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>色分け
-ライト
-UI（Start/Clear/Retry）</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>歩いてクリアできる</t>
-  </si>
-  <si>
-    <t>重力使わないと進めない</t>
-  </si>
-  <si>
-    <t>考えて進める</t>
-  </si>
-  <si>
-    <t>最初から最後まで遊べる</t>
-  </si>
-  <si>
-    <t>人に見せられる</t>
-  </si>
-  <si>
-    <t>7/16提出可能</t>
-  </si>
-  <si>
-    <t>最低限ゲーム</t>
-  </si>
-  <si>
-    <t>ゲームの核完成</t>
-  </si>
-  <si>
-    <t>ゲームらしくなる</t>
-  </si>
-  <si>
-    <t>中間発表レベル</t>
-  </si>
-  <si>
-    <t>発表可能</t>
-  </si>
-  <si>
-    <t>第1週
-~5/15</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>第2週
-~5/22</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>第3週
-~5/29</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>第4週
-~6/5</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>第5週
-~6/12</t>
-    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>エリア配置導線調整難易度調整</t>
+  </si>
+  <si>
+    <t>第5週</t>
+  </si>
+  <si>
+    <t>色分けライトUI（Start / Clear / Retry）</t>
+  </si>
+  <si>
+    <r>
+      <t>第6週</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>〜7/16</t>
+    </r>
+  </si>
+  <si>
+    <t>テストバグ修正操作感調整発表準備</t>
   </si>
 </sst>
 </file>
@@ -209,6 +188,7 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="游ゴシック"/>
@@ -239,43 +219,24 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" relativeIndent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -292,11 +253,11 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{32BEF315-DE20-45BB-8890-173EAE6730C0}" name="テーブル1" displayName="テーブル1" ref="A1:E7" totalsRowShown="0">
   <autoFilter ref="A1:E7" xr:uid="{32BEF315-DE20-45BB-8890-173EAE6730C0}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{D5B583F8-48B6-441A-8499-D5240EF1C0B1}" name="週" dataDxfId="0"/>
-    <tableColumn id="2" xr3:uid="{875C4474-4A0E-4E63-B270-CC106FA887DD}" name="目標" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{D5B583F8-48B6-441A-8499-D5240EF1C0B1}" name="週"/>
+    <tableColumn id="2" xr3:uid="{875C4474-4A0E-4E63-B270-CC106FA887DD}" name="目標"/>
     <tableColumn id="3" xr3:uid="{366487CF-AAC6-420F-9299-99C95440E170}" name="やること（詳細）"/>
-    <tableColumn id="4" xr3:uid="{C633AD49-C90D-4514-9CA6-FDDAFDA77631}" name="完成条件" dataDxfId="3"/>
-    <tableColumn id="5" xr3:uid="{9A9FF94D-8889-46E9-8DAD-17B199D63B48}" name="週末状況" dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{C633AD49-C90D-4514-9CA6-FDDAFDA77631}" name="完成条件"/>
+    <tableColumn id="5" xr3:uid="{9A9FF94D-8889-46E9-8DAD-17B199D63B48}" name="週末状況"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -609,122 +570,122 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" t="s">
-        <v>5</v>
+      <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="59.4" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B2" s="2" t="s">
+      <c r="A2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>24</v>
+      <c r="C2" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="81" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>25</v>
+      <c r="A3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="57.6" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>8</v>
+      <c r="A4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>2</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" s="5" t="s">
         <v>26</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="63.6" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>27</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="62.4" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A6" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>28</v>
+      <c r="A6" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A7" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>11</v>
+      <c r="A7" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/GRAVITY.xlsx
+++ b/GRAVITY.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ydauser01\Documents\_Git\Gravity\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D273FD88-6493-4E15-82B7-D4725CF8D03C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95947256-A907-4081-92FC-A5699AF67051}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3744" yWindow="1296" windowWidth="17280" windowHeight="10500" xr2:uid="{66840920-CFD3-4837-8A93-7C4CBF5AB457}"/>
+    <workbookView xWindow="1632" yWindow="0" windowWidth="17280" windowHeight="10500" activeTab="1" xr2:uid="{66840920-CFD3-4837-8A93-7C4CBF5AB457}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="39">
   <si>
     <t>ゲームとして最低限遊べる</t>
   </si>
@@ -100,25 +101,6 @@
   </si>
   <si>
     <t>週末状況</t>
-  </si>
-  <si>
-    <r>
-      <t>第1週</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>〜今週末</t>
-    </r>
-  </si>
-  <si>
-    <t>カメラ完成（追従・マウス視点・角度調整）仮マップ作成（Cubeのみ）ゴール判定（Trigger）</t>
   </si>
   <si>
     <t>第2週</t>
@@ -166,12 +148,40 @@
   <si>
     <t>テストバグ修正操作感調整発表準備</t>
   </si>
+  <si>
+    <t>第1週</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>カメラ完成（追従）仮マップ作成ゴール判定</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>やること（詳細）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>~7/10</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>~7/16</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>~6/26</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6/</t>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -189,6 +199,14 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="游ゴシック"/>
@@ -219,7 +237,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -230,6 +248,15 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="56" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -258,6 +285,20 @@
     <tableColumn id="3" xr3:uid="{366487CF-AAC6-420F-9299-99C95440E170}" name="やること（詳細）"/>
     <tableColumn id="4" xr3:uid="{C633AD49-C90D-4514-9CA6-FDDAFDA77631}" name="完成条件"/>
     <tableColumn id="5" xr3:uid="{9A9FF94D-8889-46E9-8DAD-17B199D63B48}" name="週末状況"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{E51F1A08-C4EF-470E-BEFF-BE33E1CF0EC0}" name="テーブル111" displayName="テーブル111" ref="A1:E7" totalsRowShown="0">
+  <autoFilter ref="A1:E7" xr:uid="{E51F1A08-C4EF-470E-BEFF-BE33E1CF0EC0}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{5F43BCB1-0782-4D8D-9327-61EB97130745}" name="週"/>
+    <tableColumn id="2" xr3:uid="{435D2660-5F60-4678-B13D-1D636B89B389}" name="目標"/>
+    <tableColumn id="3" xr3:uid="{31CB5833-4B1F-44EB-94E7-8DAF3749621D}" name="やること（詳細）"/>
+    <tableColumn id="4" xr3:uid="{72C9218C-05E3-4331-B05B-0DDD28C98470}" name="完成条件"/>
+    <tableColumn id="5" xr3:uid="{8DD70D33-70CE-474B-A9C3-D0B9EC793AEA}" name="週末状況"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -588,13 +629,13 @@
     </row>
     <row r="2" spans="1:5" ht="59.4" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>5</v>
@@ -605,13 +646,13 @@
     </row>
     <row r="3" spans="1:5" ht="81" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>6</v>
@@ -622,13 +663,13 @@
     </row>
     <row r="4" spans="1:5" ht="57.6" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>7</v>
@@ -639,13 +680,13 @@
     </row>
     <row r="5" spans="1:5" ht="63.6" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>27</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>29</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>8</v>
@@ -656,13 +697,13 @@
     </row>
     <row r="6" spans="1:5" ht="62.4" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>3</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>9</v>
@@ -673,13 +714,13 @@
     </row>
     <row r="7" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>10</v>
@@ -696,4 +737,143 @@
     <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B912A83-0B67-4BFB-85CD-3DE660AF36E8}">
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="2" max="2" width="23.796875" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="25" customWidth="1"/>
+    <col min="5" max="5" width="17.3984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A2" s="6">
+        <v>46164</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="36" x14ac:dyDescent="0.45">
+      <c r="A3" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A4" s="6">
+        <v>46192</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A5" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A6" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A7" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
 </file>
--- a/GRAVITY.xlsx
+++ b/GRAVITY.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ydauser01\Documents\_Git\Gravity\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95947256-A907-4081-92FC-A5699AF67051}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D18A8A7-D31C-429D-98D6-8A3C899E3392}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1632" yWindow="0" windowWidth="17280" windowHeight="10500" activeTab="1" xr2:uid="{66840920-CFD3-4837-8A93-7C4CBF5AB457}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" activeTab="1" xr2:uid="{66840920-CFD3-4837-8A93-7C4CBF5AB457}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="40">
   <si>
     <t>ゲームとして最低限遊べる</t>
   </si>
@@ -173,7 +173,11 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>6/</t>
+    <t>~6/19</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>~6/12</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -785,8 +789,8 @@
       </c>
     </row>
     <row r="3" spans="1:5" ht="36" x14ac:dyDescent="0.45">
-      <c r="A3" s="2" t="s">
-        <v>38</v>
+      <c r="A3" s="6" t="s">
+        <v>39</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>1</v>
@@ -802,8 +806,8 @@
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A4" s="6">
-        <v>46192</v>
+      <c r="A4" s="6" t="s">
+        <v>38</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>2</v>
@@ -872,8 +876,9 @@
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>